--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135745375</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135744588</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135745375</v>
       </c>
       <c r="B10" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135744588</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80564</v>
+        <v>80568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135745375</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135744588</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80568</v>
+        <v>80569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135745375</v>
       </c>
       <c r="B10" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135744588</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80569</v>
+        <v>80573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29800-2026 artfynd.xlsx
+++ b/artfynd/A 29800-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745683</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135744749</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135745021</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135744643</v>
       </c>
       <c r="B5" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135744742</v>
       </c>
       <c r="B6" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135745525</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135745643</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135744552</v>
       </c>
       <c r="B9" t="n">
-        <v>80573</v>
+        <v>80579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135745375</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135744588</v>
       </c>
       <c r="B11" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>135744664</v>
       </c>
       <c r="B12" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135744542</v>
       </c>
       <c r="B13" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
